--- a/feedback_surveys/030_unss_functionality_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/030_unss_functionality_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Survey header</t>
+          <t>Survey Header</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overall_satisfaction</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>improvement_ideas</t>
+          <t>Improvement Ideas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,273 +681,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>submit_button</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Contact info</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Name, email and phone fields are optional, but help us to contact you to discuss your feedback.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>name_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>name_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>email_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phone_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>phone_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submit_button</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -964,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,102 +735,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>unsatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unsatisfied</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Very satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>submit_button_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>send_email_to_submitter</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Send email to submitter</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>submit_button_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>do_not_send_email_to_submitter</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Do not send email to submitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>submit_button_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>submit_anonymously</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Submit anonymously</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
